--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484662_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484662_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.7284</v>
+        <v>12.6602</v>
       </c>
       <c r="E2" t="n">
-        <v>10.7594</v>
+        <v>11.5426</v>
       </c>
       <c r="F2" t="n">
-        <v>0.969</v>
+        <v>1.1177</v>
       </c>
       <c r="G2" t="n">
         <v>8.290900000000001</v>
@@ -610,13 +610,13 @@
         <v>3.2986</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.7953</v>
+        <v>-1.8635</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.138</v>
+        <v>-0.3548</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.6573</v>
+        <v>-1.5087</v>
       </c>
       <c r="V2" t="n">
         <v>4.7668</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.5044</v>
+        <v>6.1552</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3411</v>
+        <v>4.3139</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1634</v>
+        <v>1.8413</v>
       </c>
       <c r="G3" t="n">
         <v>3.8046</v>
@@ -688,13 +688,13 @@
         <v>2.5656</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2996</v>
+        <v>-0.0496</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0709</v>
+        <v>0.0438</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2287</v>
+        <v>-0.0934</v>
       </c>
       <c r="V3" t="n">
         <v>3.4998</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4782</v>
+        <v>2.1189</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4303</v>
+        <v>0.9223</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0479</v>
+        <v>1.1966</v>
       </c>
       <c r="G5" t="n">
         <v>2.1702</v>
@@ -844,13 +844,13 @@
         <v>2.3823</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3917</v>
+        <v>0.0324</v>
       </c>
       <c r="T5" t="n">
-        <v>0.767</v>
+        <v>0.2591</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3753</v>
+        <v>-0.2266</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6335</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3329</v>
+        <v>0.5585</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7332</v>
+        <v>0.8844</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4002</v>
+        <v>-0.3259</v>
       </c>
       <c r="G6" t="n">
         <v>0.3671</v>
@@ -922,13 +922,13 @@
         <v>1.2828</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6835</v>
+        <v>-0.458</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2202</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4633</v>
+        <v>-0.389</v>
       </c>
       <c r="V6" t="n">
         <v>-0.6335</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6299</v>
+        <v>-0.7205</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3823</v>
+        <v>-0.4234</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2476</v>
+        <v>-0.2972</v>
       </c>
       <c r="G8" t="n">
         <v>0.2402</v>
@@ -1078,13 +1078,13 @@
         <v>1.6493</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0142</v>
+        <v>-0.1048</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0905</v>
+        <v>0.0494</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1047</v>
+        <v>-0.1542</v>
       </c>
       <c r="V8" t="n">
         <v>-1.5889</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. SILVA</t>
+          <t>J. BERMEJO DORRONSORO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.701</v>
+        <v>-0.9409</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3671</v>
+        <v>-0.5463</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3339</v>
+        <v>-0.3947</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.4069</v>
+        <v>-0.373</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6216</v>
+        <v>-0.0941</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.7853</v>
+        <v>-0.279</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.7947</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0867</v>
+        <v>0.0433</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.8814</v>
+        <v>0.0417</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6122</v>
+        <v>-0.4581</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7083</v>
+        <v>-0.1374</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0961</v>
+        <v>-0.3207</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9163</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9163</v>
+        <v>0.733</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7897</v>
+        <v>-0.3846</v>
       </c>
       <c r="T9" t="n">
-        <v>1.4276</v>
+        <v>-0.0369</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.638</v>
+        <v>-0.3477</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. BERMEJO DORRONSORO</t>
+          <t>J. CARRERAS MUNOZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0951</v>
+        <v>-1.6789</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6012999999999999</v>
+        <v>-0.9294</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4937</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.373</v>
+        <v>-1.1341</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0941</v>
+        <v>-0.4482</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.279</v>
+        <v>-0.6859</v>
       </c>
       <c r="J10" t="n">
-        <v>0.08500000000000001</v>
+        <v>-0.1035</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0433</v>
+        <v>0.486</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0417</v>
+        <v>-0.5895</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4581</v>
+        <v>-1.0306</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1374</v>
+        <v>-0.9342</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3207</v>
+        <v>-0.0964</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1833</v>
+        <v>1.6493</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.733</v>
+        <v>1.6493</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5387999999999999</v>
+        <v>-1.5711</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.092</v>
+        <v>-0.2029</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4468</v>
+        <v>-1.3682</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.6231</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3219</v>
+        <v>-0.6231</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. LOPEZ ABAD</t>
+          <t>P. BAENA SANCHEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1245</v>
+        <v>-1.6851</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9479</v>
+        <v>-0.8129</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8234</v>
+        <v>-0.8722</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.4927</v>
+        <v>-2.6402</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.342</v>
+        <v>-1.3839</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1508</v>
+        <v>-1.2563</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.352</v>
+        <v>-2.4185</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7527</v>
+        <v>-0.4893</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5994</v>
+        <v>-1.9291</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1407</v>
+        <v>-0.2217</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5893</v>
+        <v>-0.8946</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4486</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>1.0995</v>
+        <v>1.8326</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.0158</v>
+        <v>1.8326</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.7209</v>
+        <v>-1.1995</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0565</v>
+        <v>0.0166</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.6643</v>
+        <v>-1.2161</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.0104</v>
+        <v>0.3219</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6231</v>
+        <v>1.5889</v>
       </c>
       <c r="X11" t="n">
-        <v>0.6127</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. BAENA SANCHEZ</t>
+          <t>E. SILVA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.3608</v>
+        <v>-1.9761</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.6372</v>
+        <v>-1.3697</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7236</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.6402</v>
+        <v>-2.4069</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.3839</v>
+        <v>-0.6216</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.2563</v>
+        <v>-1.7853</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.4185</v>
+        <v>-1.7947</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4893</v>
+        <v>0.0867</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.9291</v>
+        <v>-1.8814</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2217</v>
+        <v>-0.6122</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8946</v>
+        <v>-0.7083</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.0961</v>
       </c>
       <c r="P12" t="n">
-        <v>1.8326</v>
+        <v>0.9163</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8326</v>
+        <v>0.9163</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.8751</v>
+        <v>-0.4855</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8077</v>
+        <v>0.425</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.0674</v>
+        <v>-0.9105</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.5889</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. CARRERAS MUNOZ</t>
+          <t>G. LOPEZ ABAD</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.3966</v>
+        <v>-1.9977</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.4241</v>
+        <v>-3.0441</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9725</v>
+        <v>1.0464</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.1341</v>
+        <v>-1.4927</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4482</v>
+        <v>-1.342</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6859</v>
+        <v>-0.1508</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.1035</v>
+        <v>-1.352</v>
       </c>
       <c r="K13" t="n">
-        <v>0.486</v>
+        <v>-0.7527</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5895</v>
+        <v>-0.5994</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.0306</v>
+        <v>-0.1407</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9342</v>
+        <v>-0.5893</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0964</v>
+        <v>0.4486</v>
       </c>
       <c r="P13" t="n">
-        <v>1.6493</v>
+        <v>1.0995</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R13" t="n">
-        <v>1.6493</v>
+        <v>2.0158</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.2888</v>
+        <v>-1.5941</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6976</v>
+        <v>-0.1527</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.5912</v>
+        <v>-1.4414</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.6231</v>
+        <v>-0.0104</v>
       </c>
       <c r="W13" t="n">
         <v>-0.6231</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>0.6127</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.5416</v>
+        <v>-2.4731</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.9659</v>
+        <v>-3.7736</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4243</v>
+        <v>1.3005</v>
       </c>
       <c r="G14" t="n">
         <v>-2.0932</v>
@@ -1546,13 +1546,13 @@
         <v>0.9163</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4483</v>
+        <v>-0.3799</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5505</v>
+        <v>-0.3582</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1022</v>
+        <v>-0.0217</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,22 +1579,22 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>12.0702</v>
+        <v>12.8963</v>
       </c>
       <c r="E15" t="n">
-        <v>8.814000000000002</v>
+        <v>9.639599999999996</v>
       </c>
       <c r="F15" t="n">
-        <v>3.256499999999999</v>
+        <v>3.256599999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>7.608700000000004</v>
+        <v>7.608700000000002</v>
       </c>
       <c r="H15" t="n">
-        <v>4.883900000000002</v>
+        <v>4.883900000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>2.724699999999999</v>
+        <v>2.7247</v>
       </c>
       <c r="J15" t="n">
         <v>10.8175</v>
@@ -1603,7 +1603,7 @@
         <v>9.693099999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>1.124399999999999</v>
+        <v>1.1244</v>
       </c>
       <c r="M15" t="n">
         <v>-3.2089</v>
@@ -1615,7 +1615,7 @@
         <v>1.6003</v>
       </c>
       <c r="P15" t="n">
-        <v>8.246599999999999</v>
+        <v>8.246600000000001</v>
       </c>
       <c r="Q15" t="n">
         <v>-10.9955</v>
@@ -1624,13 +1624,13 @@
         <v>19.2419</v>
       </c>
       <c r="S15" t="n">
-        <v>-8.883900000000001</v>
+        <v>-8.058200000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.2065</v>
+        <v>-0.3806</v>
       </c>
       <c r="U15" t="n">
-        <v>-7.6774</v>
+        <v>-7.677499999999999</v>
       </c>
       <c r="V15" t="n">
         <v>5.099100000000001</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.9951</v>
+        <v>3.1288</v>
       </c>
       <c r="E16" t="n">
-        <v>4.4061</v>
+        <v>3.06</v>
       </c>
       <c r="F16" t="n">
-        <v>0.589</v>
+        <v>0.0688</v>
       </c>
       <c r="G16" t="n">
         <v>-1.2825</v>
@@ -1702,13 +1702,13 @@
         <v>1.6493</v>
       </c>
       <c r="S16" t="n">
-        <v>3.8862</v>
+        <v>2.0198</v>
       </c>
       <c r="T16" t="n">
-        <v>3.0747</v>
+        <v>1.7285</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8115</v>
+        <v>0.2913</v>
       </c>
       <c r="V16" t="n">
         <v>3.6742</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. PAREJA ANDRES</t>
+          <t>I. ALONSO QUINZA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7726</v>
+        <v>0.9424</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3759</v>
+        <v>0.7562</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1485</v>
+        <v>0.1863</v>
       </c>
       <c r="G18" t="n">
-        <v>2.1698</v>
+        <v>1.5689</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2755</v>
+        <v>-0.4732</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8943</v>
+        <v>2.042</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5946</v>
+        <v>2.2454</v>
       </c>
       <c r="K18" t="n">
-        <v>1.5015</v>
+        <v>0.2351</v>
       </c>
       <c r="L18" t="n">
-        <v>0.09320000000000001</v>
+        <v>2.0102</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5750999999999999</v>
+        <v>-0.6765</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2259</v>
+        <v>-0.7083</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8011</v>
+        <v>0.0318</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.4661</v>
+        <v>-1.8326</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.1154</v>
+        <v>-2.1991</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6493</v>
+        <v>0.3665</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3909</v>
+        <v>1.1957</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1448</v>
+        <v>0.6995</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2461</v>
+        <v>0.4962</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3219</v>
+        <v>0.0104</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.0104</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. PARDO GALLENT</t>
+          <t>P. PAREJA ANDRES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0518</v>
+        <v>0.3544</v>
       </c>
       <c r="E20" t="n">
-        <v>0.08459999999999999</v>
+        <v>-1.4721</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0328</v>
+        <v>1.8265</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7388</v>
+        <v>2.1698</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2869</v>
+        <v>1.2755</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0256</v>
+        <v>0.8943</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4519</v>
+        <v>1.5946</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4519</v>
+        <v>1.5015</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2869</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7388</v>
+        <v>-0.2259</v>
       </c>
       <c r="O20" t="n">
-        <v>1.0256</v>
+        <v>0.8011</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.5498</v>
+        <v>-1.4661</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9163</v>
+        <v>-3.1154</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3665</v>
+        <v>1.6493</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3115</v>
+        <v>-0.0273</v>
       </c>
       <c r="T20" t="n">
-        <v>0.549</v>
+        <v>0.0487</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2376</v>
+        <v>-0.076</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.4486</v>
+        <v>-0.3219</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.4486</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. ALONSO QUINZA</t>
+          <t>G. PARDO GALLENT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1503</v>
+        <v>-0.1405</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1092</v>
+        <v>-0.1077</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.041</v>
+        <v>-0.0328</v>
       </c>
       <c r="G21" t="n">
-        <v>1.5689</v>
+        <v>0.7388</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4732</v>
+        <v>-0.2869</v>
       </c>
       <c r="I21" t="n">
-        <v>2.042</v>
+        <v>1.0256</v>
       </c>
       <c r="J21" t="n">
-        <v>2.2454</v>
+        <v>0.4519</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2351</v>
+        <v>0.4519</v>
       </c>
       <c r="L21" t="n">
-        <v>2.0102</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6765</v>
+        <v>0.2869</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7083</v>
+        <v>-0.7388</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0318</v>
+        <v>1.0256</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.8326</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1991</v>
+        <v>-0.9163</v>
       </c>
       <c r="R21" t="n">
         <v>0.3665</v>
       </c>
       <c r="S21" t="n">
-        <v>0.103</v>
+        <v>0.1192</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1659</v>
+        <v>0.3567</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2689</v>
+        <v>-0.2376</v>
       </c>
       <c r="V21" t="n">
-        <v>0.0104</v>
+        <v>-0.4486</v>
       </c>
       <c r="W21" t="n">
-        <v>0.0104</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.4486</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. VERGARA APARICIO</t>
+          <t>A. ALMONACID RUBIO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2102</v>
+        <v>-0.3749</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4039</v>
+        <v>-0.3998</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1937</v>
+        <v>0.0248</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.7143</v>
+        <v>-0.3016</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6212</v>
+        <v>-0.0452</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.0931</v>
+        <v>-0.2564</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.4453</v>
+        <v>-0.5977</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3527</v>
+        <v>0.0433</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.7981</v>
+        <v>-0.641</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2689</v>
+        <v>0.2961</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9739</v>
+        <v>-0.0885</v>
       </c>
       <c r="O22" t="n">
-        <v>0.705</v>
+        <v>0.3846</v>
       </c>
       <c r="P22" t="n">
-        <v>0.3665</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0995</v>
+        <v>-0.1833</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4661</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.093</v>
+        <v>0.1099</v>
       </c>
       <c r="T22" t="n">
-        <v>2.4525</v>
+        <v>0.0592</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3595</v>
+        <v>0.0507</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9554</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3115</v>
+        <v>0.3219</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6439</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. ALMONACID RUBIO</t>
+          <t>J. VERGARA APARICIO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5454</v>
+        <v>-0.5817</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4959</v>
+        <v>-1.077</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0495</v>
+        <v>0.4953</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.3016</v>
+        <v>-1.7143</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0452</v>
+        <v>-0.6212</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2564</v>
+        <v>-1.0931</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5977</v>
+        <v>-1.4453</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0433</v>
+        <v>0.3527</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.641</v>
+        <v>-1.7981</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2961</v>
+        <v>-0.2689</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0885</v>
+        <v>-0.9739</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3846</v>
+        <v>0.705</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.1833</v>
+        <v>0.3665</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.1833</v>
+        <v>-1.0995</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.4661</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0606</v>
+        <v>1.7215</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0369</v>
+        <v>1.7794</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0236</v>
+        <v>-0.0579</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.9554</v>
       </c>
       <c r="W23" t="n">
-        <v>0.3219</v>
+        <v>-0.3115</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.3219</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.7127</v>
+        <v>-0.8467</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.737</v>
+        <v>-2.2178</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0243</v>
+        <v>1.3711</v>
       </c>
       <c r="G24" t="n">
         <v>-1.5367</v>
@@ -2326,13 +2326,13 @@
         <v>1.8326</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3029</v>
+        <v>0.1689</v>
       </c>
       <c r="T24" t="n">
-        <v>0.6026</v>
+        <v>0.1218</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2997</v>
+        <v>0.0471</v>
       </c>
       <c r="V24" t="n">
         <v>-0.945</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.3297</v>
+        <v>-0.9903</v>
       </c>
       <c r="E25" t="n">
-        <v>1.7753</v>
+        <v>2.1599</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.1049</v>
+        <v>-3.1501</v>
       </c>
       <c r="G25" t="n">
         <v>-0.4774</v>
@@ -2404,13 +2404,13 @@
         <v>0.733</v>
       </c>
       <c r="S25" t="n">
-        <v>1.7351</v>
+        <v>2.0745</v>
       </c>
       <c r="T25" t="n">
-        <v>1.0792</v>
+        <v>1.4638</v>
       </c>
       <c r="U25" t="n">
-        <v>0.6559</v>
+        <v>0.6107</v>
       </c>
       <c r="V25" t="n">
         <v>-2.0376</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.7024</v>
+        <v>-1.5028</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9939</v>
+        <v>1.0901</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.6963</v>
+        <v>-2.5929</v>
       </c>
       <c r="G26" t="n">
         <v>0.3428</v>
@@ -2482,13 +2482,13 @@
         <v>0.5498</v>
       </c>
       <c r="S26" t="n">
-        <v>0.2218</v>
+        <v>0.4214</v>
       </c>
       <c r="T26" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.1874</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1305</v>
+        <v>0.234</v>
       </c>
       <c r="V26" t="n">
         <v>-1.9005</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.9989</v>
+        <v>-1.8503</v>
       </c>
       <c r="E27" t="n">
         <v>-0.9666</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.0323</v>
+        <v>-0.8837</v>
       </c>
       <c r="G27" t="n">
         <v>-0.9081</v>
@@ -2560,13 +2560,13 @@
         <v>0.733</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.1211</v>
+        <v>0.0275</v>
       </c>
       <c r="T27" t="n">
         <v>-0.0196</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.1015</v>
+        <v>0.0471</v>
       </c>
       <c r="V27" t="n">
         <v>0.4964</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-4.059</v>
+        <v>-3.8608</v>
       </c>
       <c r="E28" t="n">
         <v>-2.9217</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.1373</v>
+        <v>-0.9391</v>
       </c>
       <c r="G28" t="n">
         <v>-3.8496</v>
@@ -2638,13 +2638,13 @@
         <v>1.0995</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.1989</v>
+        <v>-0.0007</v>
       </c>
       <c r="T28" t="n">
         <v>0.1818</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.3807</v>
+        <v>-0.1825</v>
       </c>
       <c r="V28" t="n">
         <v>-0.0104</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-9.081899999999999</v>
+        <v>-7.6076</v>
       </c>
       <c r="E29" t="n">
-        <v>-4.4067</v>
+        <v>-3.0605</v>
       </c>
       <c r="F29" t="n">
-        <v>-4.6752</v>
+        <v>-4.547</v>
       </c>
       <c r="G29" t="n">
         <v>-4.2591</v>
@@ -2716,13 +2716,13 @@
         <v>0.5498</v>
       </c>
       <c r="S29" t="n">
-        <v>0.2202</v>
+        <v>1.6946</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.276</v>
+        <v>1.0702</v>
       </c>
       <c r="U29" t="n">
-        <v>0.4962</v>
+        <v>0.6244</v>
       </c>
       <c r="V29" t="n">
         <v>-2.6606</v>
@@ -2749,16 +2749,16 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-12.0706</v>
+        <v>-11.4296</v>
       </c>
       <c r="E30" t="n">
         <v>-3.2566</v>
       </c>
       <c r="F30" t="n">
-        <v>-8.813800000000001</v>
+        <v>-8.172799999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>-7.6086</v>
+        <v>-7.608600000000001</v>
       </c>
       <c r="H30" t="n">
         <v>-4.884</v>
@@ -2767,7 +2767,7 @@
         <v>-2.7248</v>
       </c>
       <c r="J30" t="n">
-        <v>3.209000000000001</v>
+        <v>3.209</v>
       </c>
       <c r="K30" t="n">
         <v>4.809200000000001</v>
@@ -2794,13 +2794,13 @@
         <v>10.9954</v>
       </c>
       <c r="S30" t="n">
-        <v>8.884</v>
+        <v>9.524999999999999</v>
       </c>
       <c r="T30" t="n">
-        <v>7.677500000000001</v>
+        <v>7.677400000000001</v>
       </c>
       <c r="U30" t="n">
-        <v>1.2065</v>
+        <v>1.8475</v>
       </c>
       <c r="V30" t="n">
         <v>-5.099</v>
